--- a/artfynd/A 20090-2024 artfynd.xlsx
+++ b/artfynd/A 20090-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>32426</v>
       </c>
       <c r="B2" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448682.5712506982</v>
+        <v>448683</v>
       </c>
       <c r="R2" t="n">
-        <v>6166471.396598998</v>
+        <v>6166471</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,19 +757,9 @@
           <t>2010-05-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2010-05-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
